--- a/forecast_app_final/data/forecast_data.xlsx
+++ b/forecast_app_final/data/forecast_data.xlsx
@@ -9,15 +9,14 @@
   <sheets>
     <sheet name="Chat" sheetId="1" r:id="rId1"/>
     <sheet name="Phone" sheetId="2" r:id="rId2"/>
-    <sheet name="Phone59" sheetId="3" r:id="rId3"/>
-    <sheet name="Self-service" sheetId="4" r:id="rId4"/>
+    <sheet name="Self-service" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="8">
   <si>
     <t>Hour</t>
   </si>
@@ -25,28 +24,22 @@
     <t>Chat</t>
   </si>
   <si>
-    <t>Avg_for_7_days</t>
+    <t>Avg_for_6_working_days</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Chat for Aug 20–Aug 27</t>
+    <t>Forecast and Heat Map for Chat for Sep 15–Sep 22</t>
   </si>
   <si>
     <t>Phone</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Phone for Aug 20–Aug 27</t>
-  </si>
-  <si>
-    <t>Phone59</t>
-  </si>
-  <si>
-    <t>Forecast and Heat Map for Phone59 for Aug 20–Aug 27</t>
+    <t>Forecast and Heat Map for Phone for Sep 15–Sep 22</t>
   </si>
   <si>
     <t>Self-service</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Self-service for Aug 20–Aug 27</t>
+    <t>Forecast and Heat Map for Self-service for Sep 15–Sep 22</t>
   </si>
 </sst>
 </file>
@@ -444,7 +437,7 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C3">
         <v>2</v>
@@ -455,7 +448,7 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -466,7 +459,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -477,7 +470,7 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>4</v>
@@ -488,7 +481,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -502,7 +495,7 @@
         <v>36</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -513,7 +506,7 @@
         <v>53</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -521,10 +514,10 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -532,10 +525,10 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -543,10 +536,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -554,7 +547,7 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C13">
         <v>8</v>
@@ -565,7 +558,7 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -576,10 +569,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -587,10 +580,10 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -598,10 +591,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -612,7 +605,7 @@
         <v>38</v>
       </c>
       <c r="C18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -620,10 +613,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C19">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -631,10 +624,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -642,10 +635,10 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C21">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -653,10 +646,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C22">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -664,10 +657,10 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -675,7 +668,7 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -686,10 +679,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -697,10 +690,10 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -754,7 +747,7 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3">
         <v>5</v>
@@ -776,7 +769,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -787,10 +780,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -798,7 +791,7 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -809,10 +802,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C8">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -820,10 +813,10 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -831,10 +824,10 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -842,10 +835,10 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C11">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -853,10 +846,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C12">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -864,10 +857,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C13">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -878,7 +871,7 @@
         <v>74</v>
       </c>
       <c r="C14">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -886,10 +879,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C15">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -897,10 +890,10 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C16">
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -908,10 +901,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C17">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -919,10 +912,10 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -933,7 +926,7 @@
         <v>92</v>
       </c>
       <c r="C19">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -941,10 +934,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C20">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -952,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C21">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -963,10 +956,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -974,10 +967,10 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -985,10 +978,10 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C24">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -996,10 +989,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1007,7 +1000,7 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C26">
         <v>5</v>
@@ -1064,10 +1057,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1075,10 +1068,10 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1086,10 +1079,10 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1097,10 +1090,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1108,10 +1101,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>129</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1119,10 +1112,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1130,10 +1123,10 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>0</v>
+        <v>209</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1141,10 +1134,10 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1152,10 +1145,10 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1163,10 +1156,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>271</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1174,10 +1167,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>227</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1185,10 +1178,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1196,10 +1189,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>224</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1207,10 +1200,10 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1218,10 +1211,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1229,10 +1222,10 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1240,10 +1233,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>252</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1251,10 +1244,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>256</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1262,10 +1255,10 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1273,10 +1266,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1284,10 +1277,10 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>168</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1295,10 +1288,10 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1306,10 +1299,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1317,320 +1310,10 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="C26">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <conditionalFormatting sqref="C3:C26">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="B3">
-        <v>53</v>
-      </c>
-      <c r="C3">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>7</v>
-      </c>
-      <c r="B4">
-        <v>53</v>
-      </c>
-      <c r="C4">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>8</v>
-      </c>
-      <c r="B5">
-        <v>119</v>
-      </c>
-      <c r="C5">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>9</v>
-      </c>
-      <c r="B6">
-        <v>121</v>
-      </c>
-      <c r="C6">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>130</v>
-      </c>
-      <c r="C7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>167</v>
-      </c>
-      <c r="C8">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>12</v>
-      </c>
-      <c r="B9">
-        <v>212</v>
-      </c>
-      <c r="C9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>13</v>
-      </c>
-      <c r="B10">
-        <v>138</v>
-      </c>
-      <c r="C10">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>14</v>
-      </c>
-      <c r="B11">
-        <v>275</v>
-      </c>
-      <c r="C11">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>280</v>
-      </c>
-      <c r="C12">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>16</v>
-      </c>
-      <c r="B13">
-        <v>238</v>
-      </c>
-      <c r="C13">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>17</v>
-      </c>
-      <c r="B14">
-        <v>233</v>
-      </c>
-      <c r="C14">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>18</v>
-      </c>
-      <c r="B15">
-        <v>230</v>
-      </c>
-      <c r="C15">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>19</v>
-      </c>
-      <c r="B16">
-        <v>319</v>
-      </c>
-      <c r="C16">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>20</v>
-      </c>
-      <c r="B17">
-        <v>232</v>
-      </c>
-      <c r="C17">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
-        <v>21</v>
-      </c>
-      <c r="B18">
-        <v>160</v>
-      </c>
-      <c r="C18">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19">
-        <v>22</v>
-      </c>
-      <c r="B19">
-        <v>257</v>
-      </c>
-      <c r="C19">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20">
-        <v>23</v>
-      </c>
-      <c r="B20">
-        <v>254</v>
-      </c>
-      <c r="C20">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21">
-        <v>0</v>
-      </c>
-      <c r="B21">
-        <v>166</v>
-      </c>
-      <c r="C21">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22">
-        <v>1</v>
-      </c>
-      <c r="B22">
-        <v>204</v>
-      </c>
-      <c r="C22">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23">
-        <v>2</v>
-      </c>
-      <c r="B23">
-        <v>224</v>
-      </c>
-      <c r="C23">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24">
-        <v>3</v>
-      </c>
-      <c r="B24">
-        <v>154</v>
-      </c>
-      <c r="C24">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25">
-        <v>4</v>
-      </c>
-      <c r="B25">
-        <v>130</v>
-      </c>
-      <c r="C25">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26">
         <v>5</v>
-      </c>
-      <c r="B26">
-        <v>47</v>
-      </c>
-      <c r="C26">
-        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/forecast_app_final/data/forecast_data.xlsx
+++ b/forecast_app_final/data/forecast_data.xlsx
@@ -28,25 +28,25 @@
     <t>Avg_for_6_working_days</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Chat for Nov 26–Dec 03</t>
+    <t>Forecast and Heat Map for Chat for Feb 24–Mar 03</t>
   </si>
   <si>
     <t>Phone</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Phone for Nov 26–Dec 03</t>
+    <t>Forecast and Heat Map for Phone for Feb 24–Mar 03</t>
   </si>
   <si>
     <t>Phone59</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Phone59 for Nov 26–Dec 03</t>
+    <t>Forecast and Heat Map for Phone59 for Feb 24–Mar 03</t>
   </si>
   <si>
     <t>Self-service</t>
   </si>
   <si>
-    <t>Forecast and Heat Map for Self-service for Nov 26–Dec 03</t>
+    <t>Forecast and Heat Map for Self-service for Feb 24–Mar 03</t>
   </si>
 </sst>
 </file>
@@ -444,10 +444,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -455,10 +455,10 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -466,10 +466,10 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -477,10 +477,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -488,10 +488,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="C7">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -499,10 +499,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="C8">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -510,10 +510,10 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>83</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -521,10 +521,10 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -532,10 +532,10 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="C11">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -543,10 +543,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -554,10 +554,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="C13">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -565,10 +565,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -576,10 +576,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -587,10 +587,10 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -598,10 +598,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -609,10 +609,10 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -620,10 +620,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -631,10 +631,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -642,10 +642,10 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -653,10 +653,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C22">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -664,10 +664,10 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>73</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -675,10 +675,10 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -686,10 +686,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -697,10 +697,10 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -754,10 +754,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>111</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -765,10 +765,10 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>146</v>
+        <v>5</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -776,10 +776,10 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>179</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -787,10 +787,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>184</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -798,10 +798,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -809,10 +809,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>141</v>
+        <v>8</v>
       </c>
       <c r="C8">
-        <v>24</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -820,10 +820,10 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="C9">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -831,10 +831,10 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="C10">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -842,10 +842,10 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>114</v>
+        <v>35</v>
       </c>
       <c r="C11">
-        <v>19</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -853,10 +853,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="C12">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -864,10 +864,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>92</v>
+        <v>32</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -875,10 +875,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="C14">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -886,10 +886,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -897,10 +897,10 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -908,10 +908,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -919,7 +919,7 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C18">
         <v>6</v>
@@ -930,10 +930,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -941,10 +941,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C20">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -952,10 +952,10 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -963,10 +963,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="C22">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -974,10 +974,10 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -985,10 +985,10 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>104</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -996,10 +996,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>96</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1007,10 +1007,10 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>96</v>
+        <v>7</v>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1374,10 +1374,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>525</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -1385,10 +1385,10 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>526</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <v>88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -1396,10 +1396,10 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>520</v>
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>87</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1407,10 +1407,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>489</v>
+        <v>52</v>
       </c>
       <c r="C6">
-        <v>82</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1418,10 +1418,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>393</v>
+        <v>71</v>
       </c>
       <c r="C7">
-        <v>66</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1429,10 +1429,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>444</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>74</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1440,10 +1440,10 @@
         <v>12</v>
       </c>
       <c r="B9">
-        <v>461</v>
+        <v>108</v>
       </c>
       <c r="C9">
-        <v>77</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1451,10 +1451,10 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="C10">
-        <v>71</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1462,10 +1462,10 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>442</v>
+        <v>167</v>
       </c>
       <c r="C11">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1473,10 +1473,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>452</v>
+        <v>140</v>
       </c>
       <c r="C12">
-        <v>75</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1484,10 +1484,10 @@
         <v>16</v>
       </c>
       <c r="B13">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="C13">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1495,10 +1495,10 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="C14">
-        <v>55</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1506,10 +1506,10 @@
         <v>18</v>
       </c>
       <c r="B15">
-        <v>266</v>
+        <v>129</v>
       </c>
       <c r="C15">
-        <v>44</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1517,10 +1517,10 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>188</v>
+        <v>141</v>
       </c>
       <c r="C16">
-        <v>31</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -1528,10 +1528,10 @@
         <v>20</v>
       </c>
       <c r="B17">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="C17">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1539,10 +1539,10 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>193</v>
+        <v>116</v>
       </c>
       <c r="C18">
-        <v>32</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -1550,10 +1550,10 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>240</v>
+        <v>116</v>
       </c>
       <c r="C19">
-        <v>40</v>
+        <v>19</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1561,10 +1561,10 @@
         <v>23</v>
       </c>
       <c r="B20">
-        <v>276</v>
+        <v>99</v>
       </c>
       <c r="C20">
-        <v>46</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1572,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="B21">
-        <v>393</v>
+        <v>72</v>
       </c>
       <c r="C21">
-        <v>66</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1583,10 +1583,10 @@
         <v>1</v>
       </c>
       <c r="B22">
-        <v>476</v>
+        <v>60</v>
       </c>
       <c r="C22">
-        <v>79</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1594,10 +1594,10 @@
         <v>2</v>
       </c>
       <c r="B23">
-        <v>475</v>
+        <v>33</v>
       </c>
       <c r="C23">
-        <v>79</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1605,10 +1605,10 @@
         <v>3</v>
       </c>
       <c r="B24">
-        <v>563</v>
+        <v>37</v>
       </c>
       <c r="C24">
-        <v>94</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1616,10 +1616,10 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>606</v>
+        <v>3</v>
       </c>
       <c r="C25">
-        <v>101</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1627,10 +1627,10 @@
         <v>5</v>
       </c>
       <c r="B26">
-        <v>509</v>
+        <v>2</v>
       </c>
       <c r="C26">
-        <v>85</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
